--- a/data_extactor/batch_10_fa/batch_0044_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0044_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | مانیتورینگ | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | پزشکی و دندانپزشکی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | روانشناسی | اداری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | اداری | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مشکلات | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بیان کتبی | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | بینایی دور | اصالت | قدرت تنه | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | بینایی دور | اصالت | قدرت تنه | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | فضاهای بسته، با دمای کنترل‌شده | ارتباط با دیگران | ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه یا تیم کاری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق بودن یا صحت بالا | صرف زمان به حالت ایستاده | فراوانی تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | مربیان ورزشی | متخصصان قلب | تکنسین‌ها و فن‌آوران قلب و عروق | متخصصان تغذیه و رژیم‌درمانی | مربیان ورزشی و مربیان تناسب اندام گروهی | متخصصان مغز و اعصاب | کاردرمانگران | دستیاران کاردرمانی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | کمک‌کاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | پرتودرمانگران | تفریح‌درمانگران | درمانگران تنفسی | پزشکان طب ورزشی</t>
+          <t>پرستاران مراقبت‌های ویژه | مربیان ورزشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان رژیم غذایی و تغذیه | مربیان ورزشی و مدرسان تناسب اندام گروهی | متخصصان مغز و اعصاب | کاردرمانگران | کمک‌یاران کاردرمانی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | پرتودرمانگران | درمانگران تفریحی | درمانگران تنفسی | پزشکان طب ورزشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روانشناسی | پزشکی و دندانپزشکی | خدمات مشتریان و شخصی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکلات | سازماندهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | چالاکی انگشتان | ثبات دست و بازو | چالاکی دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | اشتراک زمانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | پیامد خطا | اهمیت دقیق بودن یا صحت بالا | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به حالت ایستاده | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های چهره به چهره با افراد و در تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | فضاهای بسته، با دمای کنترل‌شده | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردرمانگران | فیزیوتراپیست‌ها | تفریح‌درمانگران | درمانگران تنفسی | پرتودرمانگران | آسیب‌شناسان گفتار و زبان | هنردرمانگران | موسیقی‌درمانگران | فیزیولوژیست‌های ورزشی | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | روانشناسان بالینی و مشاوره | مربیان ورزشی | دستیاران کاردرمانی | کمک‌کاران فیزیوتراپی | مددکاران اجتماعی بخش بهداشت و درمان | متخصصان آموزش بهداشت | پزشکان تشخیص یا درمان مراقبت‌های بهداشتی، همه موارد دیگر</t>
+          <t>کاردرمانگران | فیزیوتراپیست‌ها | درمانگران تفریحی | درمانگران تنفسی | پرتودرمانگران | آسیب‌شناسان گفتار و زبان | هنردرمانگران | موسیقی‌درمانگران | فیزیولوژیست‌های ورزشی | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | روان‌شناسان بالینی و مشاوره | مربیان ورزشی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | مددکاران اجتماعی مراقبت‌های بهداشتی | متخصصان آموزش بهداشت | سایر متخصصان تشخیص یا درمان مراقبت‌های بهداشتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | مانیتورینگ | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روانشناسی | هنرهای زیبا | جامعه‌شناسی و انسان‌شناسی | خدمات مشتریان و شخصی | آموزش و پرورش | زبان انگلیسی | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | هنرهای زیبا | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مشکلات | بینایی نزدیک | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | سازماندهی اطلاعات | تشخیص رنگ‌های بصری | بینایی دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | فضاهای بسته، با دمای کنترل‌شده | ایمیل | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | کار با یا مشارکت در یک گروه یا تیم کاری | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان به حالت نشسته | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>روانشناسان بالینی و مشاوره | مددکاران اجتماعی بخش بهداشت و درمان | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | موسیقی‌درمانگران | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | کمک‌کاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌کاران روانپزشکی | تکنسین‌های روانپزشکی | روانپزشکان | تفریح‌درمانگران | مشاوران توانبخشی | روانشناسان مدرسه | آسیب‌شناسان گفتار و زبان</t>
+          <t>روان‌شناسان بالینی و مشاوره | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | موسیقی‌درمانگران | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | آسیب‌شناسان گفتار و زبان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avid Technology Pro Tools | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | نرم‌افزار سازهای مجازی | نرم‌افزار مرورگر وب</t>
+          <t>Avid Technology Pro Tools | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | نرم‌افزار ابزار مجازی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | استراتژی‌های یادگیری | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | راهبردهای یادگیری | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روانشناسی | هنرهای زیبا | زبان انگلیسی | خدمات مشتریان و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
+          <t>درمان و مشاوره | روان‌شناسی | هنرهای زیبا | زبان انگلیسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | سازماندهی اطلاعات | اصالت | توجه شنیداری | حساسیت شنوایی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | اصالت | توجه شنیداری | حساسیت شنوایی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | ایمیل | آزادی در تصمیم‌گیری | فضاهای بسته، با دمای کنترل‌شده | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روانپزشکی | هنردرمانگران | معلمان هنر، درام و موسیقی، پس از دبیرستان | روانشناسان بالینی و مشاوره | مددکاران اجتماعی بخش بهداشت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مدیران موسیقی و آهنگسازان | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌کاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | روانپزشکان | تفریح‌درمانگران | آسیب‌شناسان گفتار و زبان | دستیاران آسیب‌شناسی گفتار و زبان</t>
+          <t>پرستاران پیشرفته روانپزشکی | هنردرمانگران | مدرسان هنر، نمایش و موسیقی، آموزش عالی | روان‌شناسان بالینی و مشاوره | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مدیران موسیقی و آهنگسازان | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | آسیب‌شناسان گفتار و زبان | دستیاران آسیب‌شناسی گفتار-زبان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | علوم تجربی | تفکر انتقادی | نگارش | مانیتورینگ | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | علوم | تفکر انتقادی | نگارش | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و شخصی | زبان انگلیسی | ریاضیات | آموزش و پرورش | شیمی | پرسنل و منابع انسانی | مدیریت و سازماندهی | روانشناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | آموزش و پرورش | شیمی | پرسنل و منابع انسانی | مدیریت و اداره | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | سازماندهی اطلاعات | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | استدلال ریاضی | چالاکی انگشتان | چالاکی دست | بینایی دور | دقت کنترل | ثبات دست و بازو | سهولت کار با اعداد | اصالت | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | استدلال ریاضی | مهارت انگشتان | مهارت دستی | بینایی دور | دقت کنترل | ثبات دست و بازو | توانایی عددی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | مکالمات تلفنی | فضاهای بسته، با دمای کنترل‌شده | ارتباط با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق بودن یا صحت بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | نتایج کار و بازدهی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تابش | صرف زمان به حالت ایستاده | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تابش | موقعیت‌های تعارض</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تابش | صرف زمان برای ایستادن | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان پوست | پزشکان طب اورژانس | پزشکان عمومی داخلی | پزشکان طب طبیعی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، به جز اطفال | جراحان دهان، فک و صورت | جراحان اطفال | پزشکان اطفال، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | پزشکان طب پیشگیری | رادیولوژیست‌ها | متخصصان اورولوژی | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و فن‌آوران دامپزشکی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | پزشکان طب پیشگیری | رادیولوژیست‌ها | اورولوژیست‌ها | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Allscripts Sunrise | نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Apache Spark | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار کدگذاری تشخیصی و فرآیندی | DoctorsPartner EMR | نرم‌افزار راهنمای دارویی | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | FaceTime | FileMaker Pro | Google Docs | Google Drive | HMS | سیستم کدگذاری فرآیندهای مشترک مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Notes | Kronos Workforce Timekeeper | LinkedIn | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Taleo | PCC EHR | Per-Se Technologies ORSOS One-Call | نرم‌افزار مراقبت‌های بهداشتی PointClickCare | Prognosis Innovation Healthcare ChartAccess | QuadraMed Affinity Healthcare Information System | Siemens SIENET Sky | YouTube | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Allscripts Sunrise | نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Apache Spark | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار کدگذاری تشخیصی و فرآیندی | DoctorsPartner EMR | نرم‌افزار راهنمای دارویی | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | FaceTime | FileMaker Pro | Google Docs | Google Drive | HMS | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Notes | Kronos Workforce Timekeeper | LinkedIn | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Taleo | PCC EHR | Per-Se Technologies ORSOS One-Call | نرم‌افزار مراقبت‌های بهداشتی PointClickCare | Prognosis Innovation Healthcare ChartAccess | QuadraMed Affinity Healthcare Information System | Siemens SIENET Sky | YouTube | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | مانیتورینگ | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روانشناسی | خدمات مشتریان و شخصی | پزشکی و دندانپزشکی | زبان انگلیسی | اداری | ریاضیات | درمان و مشاوره | مدیریت و سازماندهی | آموزش و پرورش | امنیت و ایمنی عمومی | زیست‌شناسی</t>
+          <t>روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | اداری | ریاضیات | درمان و مشاوره | مدیریت و اداره | آموزش و پرورش | ایمنی و امنیت عمومی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | سازماندهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | به خاطر سپاری | روانی ایده‌ها | بینایی دور | قدرت تنه | چالاکی انگشتان | چالاکی دست | ثبات دست و بازو | اشتراک زمانی | توجه انتخابی | سرعت ادراکی | سرعت بستار | قدرت ایستا | هماهنگی چند عضو | تجسم فضایی | سهولت کار با اعداد | استدلال ریاضی | اصالت</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | حفظ کردن | روانی ایده‌ها | بینایی دور | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | سرعت ادراکی | سرعت بستار | قدرت ایستا | هماهنگی چند عضو | تجسم | توانایی عددی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | بحث‌های چهره به چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | فضاهای بسته، با دمای کنترل‌شده | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق بودن یا صحت بالا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | اهمیت تکرار وظایف مشابه | پیامد خطا | نتایج کار و بازدهی سایر کارکنان | موقعیت‌های تعارض</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | اهمیت تکرار وظایف یکسان | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان عمومی داخلی | پزشکان بیمارستان (هسپیتالیست) | پرستاران عملی و حرفه‌ای دارای مجوز | پرستاران بیهوشی | ماماها | پرستاران متخصص | دستیاران پرستاری | متخصصان زنان و زایمان | پیراپزشکان | جراحان اطفال | دستیاران پزشک</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پرستاران بیهوشی | ماماها | پرستاران متخصص | کمک‌پرستاران | متخصصان زنان و زایمان | پارامدیک‌ها | جراحان کودکان | دستیاران پزشک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | مانیتورینگ | یادگیری فعال | نگارش | گوش دادن فعال | استراتژی‌های یادگیری | علوم تجربی | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | گوش دادن فعال | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و شخصی | آموزش و پرورش | زبان انگلیسی | روانشناسی | درمان و مشاوره | مدیریت و سازماندهی | امنیت و ایمنی عمومی | زیست‌شناسی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | مدیریت و اداره | ایمنی و امنیت عمومی | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | سازماندهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | روانی ایده‌ها | تشخیص رنگ‌های بصری | اشتراک زمانی | سرعت ادراکی | به خاطر سپاری | استدلال ریاضی | اصالت</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | روانی ایده‌ها | تشخیص رنگ بصری | تقسیم توجه | سرعت ادراکی | حفظ کردن | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | بحث‌های چهره به چهره با افراد و در تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه یا تیم کاری | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق بودن یا صحت بالا | ارتباط با دیگران | نزدیکی فیزیکی | فشار زمانی | پیامد خطا | فضاهای بسته، با دمای کنترل‌شده | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به حالت ایستاده | موقعیت‌های تعارض | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | ایمیل | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت تکرار وظایف مشابه | نتایج کار و بازدهی سایر کارکنان</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | ارتباط با دیگران | نزدیکی فیزیکی | فشار زمانی | پیامد خطا | محیط داخلی، دارای کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | موقعیت‌های تعارض | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | ایمیل | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان عمومی داخلی | پرستاران عملی و حرفه‌ای دارای مجوز | پرستاران بیهوشی | ماماها | پرستاران متخصص | دستیاران پرستاری | جراحان ارتوپد، به جز اطفال | پیراپزشکان | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | پرستاران ثبت‌شده | درمانگران تنفسی</t>
+          <t>پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پرستاران بیهوشی | ماماها | پرستاران متخصص | کمک‌پرستاران | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | پرستاران ثبت‌شده | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | مانیتورینگ | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روانشناسی | درمان و مشاوره | زبان انگلیسی | پزشکی و دندانپزشکی | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | خدمات مشتریان و شخصی | قانون و حکومت | شیمی | ریاضیات | کامپیوتر و الکترونیک | مخابرات | امنیت و ایمنی عمومی | مدیریت و سازماندهی | ارتباطات و رسانه</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | پزشکی و دندان‌پزشکی | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | قانون و دولت | شیمی | ریاضیات | رایانه و الکترونیک | مخابرات | ایمنی و امنیت عمومی | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | سازماندهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | ارتباط با دیگران | صرف زمان به حالت نشسته | فضاهای بسته، با دمای کنترل‌شده | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | عصب‌روانشناسان بالینی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان عمومی داخلی | مشاوران سلامت روان | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | پزشکان اطفال، عمومی | پزشکان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | دستیاران پزشک | پزشکان طب پیشگیری | کمک‌کاران روانپزشکی | تکنسین‌های روانپزشکی | روانپزشکان | پرستاران ثبت‌شده</t>
+          <t>پرستاران مراقبت‌های ویژه | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | مشاوران سلامت روان | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | دستیاران پزشک | پزشکان طب پیشگیری | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و شخصی | روانشناسی | زبان انگلیسی | زیست‌شناسی | ریاضیات | آموزش و پرورش | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | شیمی | امنیت و ایمنی عمومی | کامپیوتر و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | ریاضیات | آموزش و پرورش | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | شیمی | ایمنی و امنیت عمومی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکلات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | سازماندهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | سرعت ادراکی | توجه انتخابی | سرعت بستار | روانی ایده‌ها | چالاکی انگشتان | انعطاف‌پذیری دسته‌بندی | اصالت | توجه شنیداری | قدرت تنه | چالاکی دست | ثبات دست و بازو | اشتراک زمانی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | سرعت ادراکی | توجه انتخابی | سرعت بستار | روانی ایده‌ها | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | اصالت | توجه شنیداری | قدرت تنه | مهارت دستی | ثبات دست و بازو | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | فضاهای بسته، با دمای کنترل‌شده | پیامد خطا | اهمیت دقیق بودن یا صحت بالا | ارتباط با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش, کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | ایمیل | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | موقعیت‌های تعارض | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به حالت ایستاده | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | اهمیت تکرار وظایف مشابه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | ایمیل | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | موقعیت‌های تعارض | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان بیمارستان (هسپیتالیست) | پرستاران عملی و حرفه‌ای دارای مجوز | پرستاران بیهوشی | ماماها | پرستاران متخصص | دستیاران پرستاری | پیراپزشکان | جراحان اطفال | پزشکان اطفال، عمومی | دستیاران پزشک | پرستاران ثبت‌شده | درمانگران تنفسی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان بیمارستانی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پرستاران بیهوشی | ماماها | پرستاران متخصص | کمک‌پرستاران | پارامدیک‌ها | جراحان کودکان | متخصصان کودکان، عمومی | دستیاران پزشک | پرستاران ثبت‌شده | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | یادگیری فعال | تفکر انتقادی | درک مطلب | مانیتورینگ | گوش دادن فعال | نگارش | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>سخن گفتن | یادگیری فعال | تفکر انتقادی | درک مطلب | نظارت | گوش دادن فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | آموزش و پرورش | روانشناسی | زبان انگلیسی | زیست‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتریان و شخصی | مدیریت و سازماندهی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | آموزش و پرورش | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | روانی ایده‌ها | بینایی دور | اشتراک زمانی | سرعت ادراکی | سرعت بستار | سهولت کار با اعداد | اصالت | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | روانی ایده‌ها | بینایی دور | تقسیم توجه | سرعت ادراکی | سرعت بستار | توانایی عددی | اصالت | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره به چهره با افراد و در تیم‌ها | فضاهای بسته، با دمای کنترل‌شده | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق بودن یا صحت بالا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نتایج کار و بازدهی سایر کارکنان | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | پیامد خطا | سلامت و ایمنی سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | موقعیت‌های تعارض</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | پیامد خطا | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان قلب | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان عمومی داخلی | متخصصان انفورماتیک سلامت | پزشکان بیمارستان (هسپیتالیست) | پرستاران عملی و حرفه‌ای دارای مجوز | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | پیراپزشکان | جراحان اطفال | پزشکان اطفال، عمومی | دستیاران پزشک | تکنسین‌های روانپزشکی | روانپزشکان | پرستاران ثبت‌شده</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان قلب | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان انفورماتیک سلامت | پزشکان بیمارستانی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | پارامدیک‌ها | جراحان کودکان | متخصصان کودکان، عمومی | دستیاران پزشک | تکنسین‌های روانپزشکی | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0044_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0044_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | درمان و مشاوره | آموزش و تدریس | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | امور اداری و دفتری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | اداری | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | روانی ایده‌ها | دید دور | ابتکار | قدرت تنه | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | بینایی دور | اصالت | قدرت تنه | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | مربیان بدنسازی و آمادگی جسمانی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | کارشناسان تغذیه و رژیم‌درمانی | مربیان ورزشی و مربیان آمادگی جسمانی گروهی | متخصصان مغز و اعصاب | کاردرمانگران | کمک‌کاردرمانگران | جراحان ارتوپد، به‌جز اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپ‌ها | تکنسین‌های روانپزشکی | پرتودرمانگران | تفریح‌درمانگران | تنفس‌درمانگران | متخصصان پزشکی ورزشی</t>
+          <t>پرستاران مراقبت‌های حاد | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مربیان ورزش و آمادگی جسمانی گروهی | متخصصان مغز و اعصاب | کاردرمانگران | کمک‌یاران کاردرمانی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روان‌پزشکی و بهداشت روان | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | پزشکان طب ورزشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تصویرسازی ذهنی | تقسیم توجه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردرمانگران | فیزیوتراپ‌ها | تفریح‌درمانگران | تنفس‌درمانگران | پرتودرمانگران | گفتاردرمانگران | هنر‌درمانگران | موسیقی‌درمانگران | فیزیولوژیست‌های ورزشی | درمانگران کم‌بینایی، کارشناسان جهت‌یابی و حرکت و درمانگران توانبخشی بینایی | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | روان‌شناسان بالینی و مشاور | مربیان بدنسازی و آمادگی جسمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | مددکاران اجتماعی بخش سلامت | کارشناسان آموزش بهداشت | سایر متخصصان تشخیص و درمان حوزه سلامت</t>
+          <t>کاردرمانگران | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | پرتودرمانگران / کارشناسان رادیوتراپی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | هنر‌درمانگران | موسیقی‌درمانگران | فیزیولوژیست‌های ورزشی | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | روان‌شناسان بالینی و مشاوران سلامت روان | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | کاردان‌های کاردرمانی | کاردان‌های فیزیوتراپی | مددکاران اجتماعی بخش سلامت و درمان | کارشناسان آموزش بهداشت و ارتقای سلامت | سایر متخصصان تشخیص و درمان حوزه سلامت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | هنرهای تجسمی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | هنرهای زیبا | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | ابتکار | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تصویرسازی ذهنی | مرتب‌سازی اطلاعات | تمایز رنگ‌ها | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاور | مددکاران اجتماعی بخش سلامت | درمانگران کم‌بینایی، کارشناسان جهت‌یابی و حرکت و درمانگران توانبخشی بینایی | مشاوران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | موسیقی‌درمانگران | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | دستیاران فیزیوتراپی | فیزیوتراپ‌ها | بهیاران روانپزشکی | تکنسین‌های روانپزشکی | روانپزشکان | تفریح‌درمانگران | مشاوران توانبخشی | روان‌شناسان مدرسه | گفتاردرمانگران</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | مددکاران اجتماعی بخش سلامت و درمان | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | درمانگران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | موسیقی‌درمانگران | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدارس | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avid Technology Pro Tools | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار پروتکل صوتی ابزار دیجیتال MIDI | نرم‌افزار سازهای مجازی | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب</t>
+          <t>Avid Technology Pro Tools | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | نرم‌افزار ابزار مجازی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | راهبردهای یادگیری | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | راهبردهای یادگیری | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | هنرهای تجسمی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس</t>
+          <t>درمان و مشاوره | روان‌شناسی | هنرهای زیبا | زبان انگلیسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | مرتب‌سازی اطلاعات | ابتکار | توجه شنیداری | حساسیت شنیداری | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | اصالت | توجه شنیداری | حساسیت شنوایی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روانپزشکی | هنر‌درمانگران | مدرسان هنر، نمایش و موسیقی در آموزش عالی | روان‌شناسان بالینی و مشاور | مددکاران اجتماعی بخش سلامت | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | رهبران ارکستر و آهنگسازان | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپ‌ها | تکنسین‌های روانپزشکی | روانپزشکان | تفریح‌درمانگران | گفتاردرمانگران | دستیاران گفتاردرمانی</t>
+          <t>پرستاران تخصصی روانپزشکی | هنر‌درمانگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | روان‌شناسان بالینی و مشاوران سلامت روان | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | رهبران ارکستر، مدیران موسیقی و آهنگسازان | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | یادگیری فعال | سخن گفتن | علوم تجربی | تفکر انتقادی | نگارش | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | علوم | تفکر انتقادی | نگارش | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | آموزش و تدریس | شیمی | امور کارکنان و منابع انسانی | مدیریت و امور اداری | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | آموزش و پرورش | شیمی | پرسنل و منابع انسانی | مدیریت و اداره | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | مرتب‌سازی اطلاعات | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در نتیجه‌گیری | توجه انتخابی | استدلال ریاضی | چابکی انگشتان | چابکی دستی | دید دور | دقت کنترل | ثبات دست و بازو | مهارت محاسبات | ابتکار | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | استدلال ریاضی | مهارت انگشتان | مهارت دستی | بینایی دور | دقت کنترل | ثبات دست و بازو | توانایی عددی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان پوست و مو | متخصصان طب اورژانس | متخصصان بیماری‌های داخلی | پزشکان طب سنتی و مکمل | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز اطفال | جراحان دهان، فک و صورت | جراحان اطفال | متخصصان کودکان و اطفال | متخصصان طب فیزیکی و توانبخشی | آسیب‌شناسان (پاتولوژیست‌ها) | متخصصان طب پیشگیری و پزشکی اجتماعی | رادیولوژیست‌ها | متخصصان اورولوژی | کارگران نگهداری حیوانات آزمایشگاهی و کمک‌دامپزشکان | تکنسین‌ها و کارشناسان دامپزشکی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | متخصصان پزشکی اجتماعی و طب پیشگیری | متخصصان رادیولوژی | متخصصان اورولوژی | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | زبان انگلیسی | امور اداری و دفتری | ریاضیات | درمان و مشاوره | مدیریت و امور اداری | آموزش و تدریس | ایمنی و امنیت عمومی | زیست‌شناسی</t>
+          <t>روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | اداری | ریاضیات | درمان و مشاوره | مدیریت و اداره | آموزش و پرورش | ایمنی و امنیت عمومی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در نتیجه‌گیری | حفظ کردن | روانی ایده‌ها | دید دور | قدرت تنه | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | سرعت ادراک | سرعت در نتیجه‌گیری | قدرت ایستا | هماهنگی اندام‌ها | تصویرسازی ذهنی | مهارت محاسبات | استدلال ریاضی | ابتکار</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | حفظ کردن | روانی ایده‌ها | بینایی دور | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | سرعت ادراکی | سرعت بستار | قدرت ایستا | هماهنگی چند عضو | تجسم | توانایی عددی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه (ICU/CCU) | تکنسین‌های فوریت‌های پزشکی | متخصصان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان هوشبری | ماماها | پرستاران متخصص | کمک‌بهیاران | متخصصان زنان و زایمان | کارشناسان فوریت‌های پزشکی (پارامدیک‌ها) | جراحان اطفال | دستیاران پزشک</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | ماماهای پرستار | پرستاران بالینی پیشرفته | کمک‌پرستاران | متخصصان زنان و زایمان | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | دستیاران پزشک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | شنیدن فعال | راهبردهای یادگیری | علوم تجربی | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | گوش دادن فعال | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | مدیریت و امور اداری | ایمنی و امنیت عمومی | زیست‌شناسی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | مدیریت و اداره | ایمنی و امنیت عمومی | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در نتیجه‌گیری | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | سرعت در نتیجه‌گیری | روانی ایده‌ها | تمایز رنگ‌ها | تقسیم توجه | سرعت ادراک | حفظ کردن | استدلال ریاضی | ابتکار</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | روانی ایده‌ها | تشخیص رنگ بصری | تقسیم توجه | سرعت ادراکی | حفظ کردن | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه (ICU/CCU) | تکنسین‌های فوریت‌های پزشکی | متخصصان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان هوشبری | ماماها | پرستاران متخصص | کمک‌بهیاران | جراحان ارتوپد، به‌جز اطفال | کارشناسان فوریت‌های پزشکی (پارامدیک‌ها) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پرستاران | تنفس‌درمانگران</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | ماماهای پرستار | پرستاران بالینی پیشرفته | کمک‌پرستاران | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | پزشکی و دندانپزشکی | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | شیمی | ریاضیات | رایانه و الکترونیک | مخابرات و ارتباطات | ایمنی و امنیت عمومی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | پزشکی و دندان‌پزشکی | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | قانون و دولت | شیمی | ریاضیات | رایانه و الکترونیک | مخابرات | ایمنی و امنیت عمومی | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | ابتکار | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | عصب‌روان‌شناسان بالینی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه (ICU/CCU) | متخصصان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | مشاوران سلامت روان | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان کودکان و اطفال | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپ‌ها | دستیاران پزشک | متخصصان طب پیشگیری و پزشکی اجتماعی | بهیاران روانپزشکی | تکنسین‌های روانپزشکی | روانپزشکان | پرستاران</t>
+          <t>پرستاران مراقبت‌های حاد | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | مشاوران سلامت روان | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | دستیاران پزشک | متخصصان پزشکی اجتماعی و طب پیشگیری | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم تجربی</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | ریاضیات | آموزش و تدریس | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | شیمی | ایمنی و امنیت عمومی | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | ریاضیات | آموزش و پرورش | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | شیمی | ایمنی و امنیت عمومی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در نتیجه‌گیری | دید نزدیک | سرعت ادراک | توجه انتخابی | سرعت در نتیجه‌گیری | روانی ایده‌ها | چابکی انگشتان | انعطاف‌پذیری در طبقه‌بندی | ابتکار | توجه شنیداری | قدرت تنه | چابکی دستی | ثبات دست و بازو | تقسیم توجه</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | سرعت ادراکی | توجه انتخابی | سرعت بستار | روانی ایده‌ها | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | اصالت | توجه شنیداری | قدرت تنه | مهارت دستی | ثبات دست و بازو | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران متخصص بالینی | متخصصان طب اورژانس | پزشکان خانواده | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان هوشبری | ماماها | پرستاران متخصص | کمک‌بهیاران | کارشناسان فوریت‌های پزشکی (پارامدیک‌ها) | جراحان اطفال | متخصصان کودکان و اطفال | دستیاران پزشک | پرستاران | تنفس‌درمانگران</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | ماماهای پرستار | پرستاران بالینی پیشرفته | کمک‌پرستاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان عمومی کودکان | دستیاران پزشک | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | یادگیری فعال | تفکر انتقادی | درک مطلب | نظارت | شنیدن فعال | نگارش | راهبردهای یادگیری | علوم تجربی</t>
+          <t>سخن گفتن | یادگیری فعال | تفکر انتقادی | درک مطلب | نظارت | گوش دادن فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | آموزش و تدریس | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | آموزش و پرورش | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | توجه انتخابی | روانی ایده‌ها | دید دور | تقسیم توجه | سرعت ادراک | سرعت در نتیجه‌گیری | مهارت محاسبات | ابتکار | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | روانی ایده‌ها | بینایی دور | تقسیم توجه | سرعت ادراکی | سرعت بستار | توانایی عددی | اصالت | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان قلب و عروق | پرستاران مراقبت‌های ویژه (ICU/CCU) | متخصصان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | کارشناسان انفورماتیک سلامت | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | کارشناسان فوریت‌های پزشکی (پارامدیک‌ها) | جراحان اطفال | متخصصان کودکان و اطفال | دستیاران پزشک | تکنسین‌های روانپزشکی | روانپزشکان | پرستاران</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیماری‌های قلب و عروق | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان انفورماتیک سلامت | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان عمومی کودکان | دستیاران پزشک | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
